--- a/ig/ch-elm/ValueSet-ch-elm-results-component-gene-cpe.xlsx
+++ b/ig/ch-elm/ValueSet-ch-elm-results-component-gene-cpe.xlsx
@@ -29,7 +29,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.13.1</t>
+    <t>1.14.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -59,7 +59,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-01-21T11:21:00+00:00</t>
+    <t>2026-05-26T14:58:40+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/ch-elm/ValueSet-ch-elm-results-component-gene-cpe.xlsx
+++ b/ig/ch-elm/ValueSet-ch-elm-results-component-gene-cpe.xlsx
@@ -29,7 +29,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.14.0</t>
+    <t>1.14.1</t>
   </si>
   <si>
     <t>Name</t>
@@ -59,7 +59,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-26T14:58:40+00:00</t>
+    <t>2026-07-01T19:23:08+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/ch-elm/ValueSet-ch-elm-results-component-gene-cpe.xlsx
+++ b/ig/ch-elm/ValueSet-ch-elm-results-component-gene-cpe.xlsx
@@ -7,12 +7,13 @@
   </bookViews>
   <sheets>
     <sheet name="Metadata" r:id="rId3" sheetId="1"/>
+    <sheet name="Include #0" r:id="rId4" sheetId="2"/>
   </sheets>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="29" uniqueCount="29">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="105" uniqueCount="103">
   <si>
     <t>Property</t>
   </si>
@@ -29,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.14.1</t>
+    <t>1.15.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -41,7 +42,7 @@
     <t>Title</t>
   </si>
   <si>
-    <t>CH ELM Results Component Gene CPE</t>
+    <t>CH ELM Results Gene Cpe</t>
   </si>
   <si>
     <t>Status</t>
@@ -59,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-01T19:23:08+00:00</t>
+    <t>2026-08-12T07:20:00+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -83,7 +84,7 @@
     <t>Description</t>
   </si>
   <si>
-    <t>The "CH ELM Results Component Gene CPE" provides a curated set of codes representing specific genes.</t>
+    <t>The "CH ELM Results Gene Cpe" group provides a curated set of codes representing specific genotypes. Each code within this group is selected to ensure consistency and accuracy for medical coding related to the primary LOINC codes. Clients using the "CH ELM Results Gene Cpe" group should refer to the provided codes to ensure they capture and report antibiotic information correctly and consistently</t>
   </si>
   <si>
     <t>Purpose</t>
@@ -99,6 +100,228 @@
   </si>
   <si>
     <t>BooleanType[null]</t>
+  </si>
+  <si>
+    <t>Concept</t>
+  </si>
+  <si>
+    <t>85829-0</t>
+  </si>
+  <si>
+    <t>Carbapenem resistance blaSPM gene [Presence] by Molecular method</t>
+  </si>
+  <si>
+    <t>85823-3</t>
+  </si>
+  <si>
+    <t>Carbapenem resistance blaGES gene [Presence] by Molecular method</t>
+  </si>
+  <si>
+    <t>85826-6</t>
+  </si>
+  <si>
+    <t>Carbapenem resistance blaOXA-24-like gene [Presence] by Molecular method</t>
+  </si>
+  <si>
+    <t>105019-4</t>
+  </si>
+  <si>
+    <t>Bacterial Carbapenem resistance blaNDM-1 gene [Presence] by Molecular method</t>
+  </si>
+  <si>
+    <t>105028-5</t>
+  </si>
+  <si>
+    <t>Bacterial Carbapenem resistance blaOXA-232 gene [Presence] by Molecular method</t>
+  </si>
+  <si>
+    <t>73982-1</t>
+  </si>
+  <si>
+    <t>Carbapenem resistance blaNDM gene [Presence] by Molecular method</t>
+  </si>
+  <si>
+    <t>105034-3</t>
+  </si>
+  <si>
+    <t>Bacterial Carbapenem resistance blaVIM-1 gene [Presence] by Molecular method</t>
+  </si>
+  <si>
+    <t>LP113695-3</t>
+  </si>
+  <si>
+    <t>Carbapenem resistance genes</t>
+  </si>
+  <si>
+    <t>105021-0</t>
+  </si>
+  <si>
+    <t>Bacterial Carbapenem resistance blaNDM-4 gene [Presence] by Molecular method</t>
+  </si>
+  <si>
+    <t>105029-3</t>
+  </si>
+  <si>
+    <t>Bacterial Carbapenem resistance blaOXA24/40 gene [Presence] by Molecular method</t>
+  </si>
+  <si>
+    <t>85827-4</t>
+  </si>
+  <si>
+    <t>Carbapenem resistance bla OXA-48-like gene [Presence] by Molecular method</t>
+  </si>
+  <si>
+    <t>105022-8</t>
+  </si>
+  <si>
+    <t>Bacterial Carbapenem resistance blaNDM-5 gene [Presence] by Molecular method</t>
+  </si>
+  <si>
+    <t>105020-2</t>
+  </si>
+  <si>
+    <t>Bacterial Carbapenem resistance blaNDM-19 gene [Presence] by Molecular method</t>
+  </si>
+  <si>
+    <t>101123-8</t>
+  </si>
+  <si>
+    <t>Bacterial carbapenem resistance blaIMI gene [Presence] by Molecular method</t>
+  </si>
+  <si>
+    <t>85825-8</t>
+  </si>
+  <si>
+    <t>Carbapenem resistance blaOXA-23-like gene [Presence] by Molecular method</t>
+  </si>
+  <si>
+    <t>105018-6</t>
+  </si>
+  <si>
+    <t>Bacterial Carbapenem resistance blaKPC-3 gene [Presence] by Molecular method</t>
+  </si>
+  <si>
+    <t>85501-5</t>
+  </si>
+  <si>
+    <t>Carbapenem resistance blaVIM gene [Presence] by Molecular method</t>
+  </si>
+  <si>
+    <t>105030-1</t>
+  </si>
+  <si>
+    <t>Bacterial Carbapenem resistance blaOXA-244 gene [Presence] by Molecular method</t>
+  </si>
+  <si>
+    <t>105015-2</t>
+  </si>
+  <si>
+    <t>Bacterial Carbapenem resistance blaGIM-1 gene [Presence] by Molecular method</t>
+  </si>
+  <si>
+    <t>85503-1</t>
+  </si>
+  <si>
+    <t>Carbapenem resistance blaOXA-48 gene [Presence] by Molecular method</t>
+  </si>
+  <si>
+    <t>105014-5</t>
+  </si>
+  <si>
+    <t>Bacterial Carbapenem resistance blaGES-5 gene [Presence] by Molecular method</t>
+  </si>
+  <si>
+    <t>105031-9</t>
+  </si>
+  <si>
+    <t>Bacterial Carbapenem resistance blaOXA-58 gene [Presence] by Molecular method</t>
+  </si>
+  <si>
+    <t>105035-0</t>
+  </si>
+  <si>
+    <t>Bacterial Carbapenem resistance blaVIM-2 gene [Presence] by Molecular method</t>
+  </si>
+  <si>
+    <t>105036-8</t>
+  </si>
+  <si>
+    <t>Bacterial Carbapenem resistance blaVIM-4 gene [Presence] by Molecular method</t>
+  </si>
+  <si>
+    <t>85498-4</t>
+  </si>
+  <si>
+    <t>Carbapenem resistance blaIMP gene [Presence] by Molecular method</t>
+  </si>
+  <si>
+    <t>105023-6</t>
+  </si>
+  <si>
+    <t>Bacterial Carbapenem resistance blaNDM-7 gene [Presence] by Molecular method</t>
+  </si>
+  <si>
+    <t>85828-2</t>
+  </si>
+  <si>
+    <t>Carbapenem resistance blaOXA-58-like gene [Presence] by Molecular method</t>
+  </si>
+  <si>
+    <t>105027-7</t>
+  </si>
+  <si>
+    <t>Bacterial Carbapenem resistance blaOXA-23 gene [Presence] by Molecular method</t>
+  </si>
+  <si>
+    <t>105032-7</t>
+  </si>
+  <si>
+    <t>Bacterial Carbapenem resistance blaOXA-72 gene [Presence] by Molecular method</t>
+  </si>
+  <si>
+    <t>105025-1</t>
+  </si>
+  <si>
+    <t>Bacterial Carbapenem resistance blaOXA 181 gene [Presence] by Molecular method</t>
+  </si>
+  <si>
+    <t>49617-4</t>
+  </si>
+  <si>
+    <t>Carbapenem resistance blaKPC gene [Presence] by Molecular method</t>
+  </si>
+  <si>
+    <t>105024-4</t>
+  </si>
+  <si>
+    <t>Bacterial Carbapenem resistance blaNDM-9 gene [Presence] by Molecular method</t>
+  </si>
+  <si>
+    <t>85833-2</t>
+  </si>
+  <si>
+    <t>Carbapenem resistance blaGIM gene [Presence] by Molecular method</t>
+  </si>
+  <si>
+    <t>105026-9</t>
+  </si>
+  <si>
+    <t>Bacterial Carbapenem resistance blaOXA-162 gene [Presence] by Molecular method</t>
+  </si>
+  <si>
+    <t>105017-8</t>
+  </si>
+  <si>
+    <t>Bacterial Carbapenem resistance blaKPC-2 gene [Presence] by Molecular method</t>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t>System URI</t>
+  </si>
+  <si>
+    <t>http://loinc.org</t>
   </si>
 </sst>
 </file>
@@ -360,4 +583,322 @@
   </sheetData>
   <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <dimension ref="A1:B38"/>
+  <sheetFormatPr defaultRowHeight="15.0"/>
+  <cols>
+    <col min="1" max="1" width="30.703125" customWidth="true"/>
+    <col min="2" max="2" width="50.703125" customWidth="true"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="s" s="1">
+        <v>29</v>
+      </c>
+      <c r="B1" t="s" s="1">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="s" s="2">
+        <v>30</v>
+      </c>
+      <c r="B2" t="s" s="2">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="s" s="2">
+        <v>32</v>
+      </c>
+      <c r="B3" t="s" s="2">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="s" s="2">
+        <v>34</v>
+      </c>
+      <c r="B4" t="s" s="2">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="s" s="2">
+        <v>36</v>
+      </c>
+      <c r="B5" t="s" s="2">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="s" s="2">
+        <v>38</v>
+      </c>
+      <c r="B6" t="s" s="2">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="s" s="2">
+        <v>40</v>
+      </c>
+      <c r="B7" t="s" s="2">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="s" s="2">
+        <v>42</v>
+      </c>
+      <c r="B8" t="s" s="2">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="s" s="2">
+        <v>44</v>
+      </c>
+      <c r="B9" t="s" s="2">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="s" s="2">
+        <v>46</v>
+      </c>
+      <c r="B10" t="s" s="2">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="s" s="2">
+        <v>48</v>
+      </c>
+      <c r="B11" t="s" s="2">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="s" s="2">
+        <v>50</v>
+      </c>
+      <c r="B12" t="s" s="2">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="s" s="2">
+        <v>52</v>
+      </c>
+      <c r="B13" t="s" s="2">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="s" s="2">
+        <v>54</v>
+      </c>
+      <c r="B14" t="s" s="2">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="s" s="2">
+        <v>56</v>
+      </c>
+      <c r="B15" t="s" s="2">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="s" s="2">
+        <v>58</v>
+      </c>
+      <c r="B16" t="s" s="2">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="s" s="2">
+        <v>60</v>
+      </c>
+      <c r="B17" t="s" s="2">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="s" s="2">
+        <v>62</v>
+      </c>
+      <c r="B18" t="s" s="2">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="s" s="2">
+        <v>64</v>
+      </c>
+      <c r="B19" t="s" s="2">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="s" s="2">
+        <v>66</v>
+      </c>
+      <c r="B20" t="s" s="2">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="s" s="2">
+        <v>68</v>
+      </c>
+      <c r="B21" t="s" s="2">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="s" s="2">
+        <v>70</v>
+      </c>
+      <c r="B22" t="s" s="2">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="B23" t="s" s="2">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="B24" t="s" s="2">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="B25" t="s" s="2">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="B26" t="s" s="2">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="B27" t="s" s="2">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="B28" t="s" s="2">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="B29" t="s" s="2">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="s" s="2">
+        <v>86</v>
+      </c>
+      <c r="B30" t="s" s="2">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="B31" t="s" s="2">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="B32" t="s" s="2">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="s" s="2">
+        <v>92</v>
+      </c>
+      <c r="B33" t="s" s="2">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="s" s="2">
+        <v>94</v>
+      </c>
+      <c r="B34" t="s" s="2">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="s" s="2">
+        <v>96</v>
+      </c>
+      <c r="B35" t="s" s="2">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="s" s="2">
+        <v>98</v>
+      </c>
+      <c r="B36" t="s" s="2">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="s" s="2">
+        <v>100</v>
+      </c>
+      <c r="B37" t="s" s="2">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="s" s="2">
+        <v>101</v>
+      </c>
+      <c r="B38" t="s" s="2">
+        <v>102</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
+</worksheet>
 </file>
--- a/ig/ch-elm/ValueSet-ch-elm-results-component-gene-cpe.xlsx
+++ b/ig/ch-elm/ValueSet-ch-elm-results-component-gene-cpe.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.15.0</t>
+    <t>1.15.1</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-12T07:20:00+00:00</t>
+    <t>2026-08-14T07:34:39+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
